--- a/reports/jobs_2026-09-02.xlsx
+++ b/reports/jobs_2026-09-02.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Platform and Application Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://careers.arm.com/job/cambridge/platform-and-application-engineer/33099/99763341920</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1031,7 +1031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1039,12 +1043,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1056,17 +1060,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Embedded Compiler Engineer (Machine Learning)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1082,12 +1086,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/embedded-compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1099,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1117,11 +1121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,12 +1146,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Cloudflare India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Customer Engineer, India (Based in Mumbai)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1164,7 +1164,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1172,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1189,12 +1193,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1207,7 +1211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1215,12 +1223,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1232,12 +1240,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Cloudflare India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Customer Engineer, India (Based in Mumbai)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1252,7 +1260,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Remote India</t>
+          <t>Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1262,12 +1270,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1279,17 +1287,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1299,7 +1307,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1309,12 +1317,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1331,12 +1339,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1356,7 +1364,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1378,12 +1386,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1393,7 +1401,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru/ Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1403,7 +1411,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1425,12 +1433,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1450,7 +1458,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1472,12 +1480,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1487,7 +1495,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru/ Gurgaon Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1497,7 +1505,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1519,7 +1527,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1544,7 +1552,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,12 +1574,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 (Full Stack)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1581,7 +1589,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1591,7 +1599,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1613,7 +1621,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1638,7 +1646,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1660,7 +1668,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1675,7 +1683,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1685,7 +1693,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1707,12 +1715,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1754,7 +1762,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1769,7 +1777,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1779,7 +1787,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1801,12 +1809,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1816,7 +1824,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1848,12 +1856,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1873,7 +1881,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1890,17 +1898,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1910,7 +1918,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1920,12 +1928,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1937,17 +1945,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1957,7 +1965,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1967,12 +1975,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1989,7 +1997,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2014,7 +2022,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2031,17 +2039,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2049,11 +2057,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2061,12 +2065,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2078,17 +2082,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2096,11 +2100,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2125,17 +2125,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2143,11 +2143,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2155,12 +2151,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2172,17 +2168,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2190,7 +2186,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, in</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2215,12 +2215,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2258,17 +2258,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2276,11 +2276,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2288,12 +2284,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2305,12 +2301,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2323,11 +2319,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2335,12 +2327,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2352,17 +2344,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2372,7 +2364,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2382,12 +2374,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2404,12 +2396,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2419,7 +2411,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2429,7 +2421,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2446,17 +2438,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2466,7 +2458,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2476,12 +2468,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2493,17 +2485,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2511,7 +2503,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2519,12 +2515,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2536,17 +2532,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2554,7 +2550,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2579,17 +2579,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2622,17 +2622,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2665,12 +2665,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2683,11 +2683,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2695,12 +2691,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2712,17 +2708,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2738,12 +2734,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2755,17 +2751,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2773,7 +2769,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2798,17 +2798,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Intern - Admin and Operations</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2816,11 +2816,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2828,12 +2824,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/eea11d47-b37b-444f-aed9-ffc972e4c321</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2845,12 +2841,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2863,11 +2859,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -2875,12 +2867,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2897,7 +2889,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Intern - Admin and Operations</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/eea11d47-b37b-444f-aed9-ffc972e4c321</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2944,7 +2936,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2954,12 +2946,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2969,7 +2961,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2991,7 +2983,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3016,7 +3008,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3033,25 +3025,29 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+          <t>recent graduate</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3059,12 +3055,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3076,17 +3072,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3096,7 +3092,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3106,12 +3102,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3123,12 +3119,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3141,11 +3137,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3153,12 +3145,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3175,7 +3167,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3200,7 +3192,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3217,17 +3209,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3235,7 +3227,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3243,12 +3239,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3260,17 +3256,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3280,7 +3276,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3290,12 +3286,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3307,17 +3303,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3325,11 +3321,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3337,12 +3329,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3354,12 +3346,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3374,7 +3366,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3384,12 +3376,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3401,17 +3393,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3421,7 +3413,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3431,12 +3423,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3448,17 +3440,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Product Operations &amp; Analytics Intern</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3468,7 +3460,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3478,12 +3470,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3495,17 +3487,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3515,7 +3507,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3525,12 +3517,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3542,12 +3534,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Product Operations &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3560,7 +3552,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3568,12 +3564,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3585,17 +3581,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3603,7 +3599,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3714,17 +3714,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3732,11 +3732,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3744,12 +3740,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3761,17 +3757,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3779,11 +3775,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3791,12 +3783,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3808,17 +3800,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3828,7 +3820,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3838,12 +3830,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3855,17 +3847,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3873,7 +3865,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3881,12 +3877,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3898,17 +3894,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3918,7 +3914,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3928,12 +3924,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3945,17 +3941,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3963,11 +3959,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -3975,12 +3967,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3992,17 +3984,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4012,7 +4004,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4022,12 +4014,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4039,52 +4031,146 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>Zscaler India</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Software Development Engineer</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>1 - 3 years</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Bangalore, IND</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4164,6 +4250,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4175,7 +4263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4263,19 +4351,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ather Energy</t>
+          <t>Capillary Technologies</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.atherenergy.com/careers</t>
+          <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -4343,19 +4431,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OYO</t>
+          <t>Netcore Cloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.oyorooms.com/careers/</t>
+          <t>https://netcorecloud.com/careers/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+  - navigating to "https://netcorecloud.com/careers/", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -4383,35 +4471,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shiprocket</t>
+          <t>Coforge</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.shiprocket.in/careers/</t>
+          <t>https://www.coforge.com/careers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4420,18 +4488,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4440,18 +4508,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
